--- a/www/flightdata/xlsx/eoss-381.xlsx
+++ b/www/flightdata/xlsx/eoss-381.xlsx
@@ -3771,7 +3771,7 @@
         <v>28844.14</v>
       </c>
       <c r="I2">
-        <v>778</v>
+        <v>492</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
